--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-patient-ins.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-patient-ins.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$223</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7952" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8286" uniqueCount="920">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1326,28 +1326,28 @@
     <t>PID-3</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS</t>
-  </si>
-  <si>
-    <t>NSS</t>
+    <t>Patient.identifier:NSS-NIR</t>
+  </si>
+  <si>
+    <t>NSS-NIR</t>
   </si>
   <si>
     <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIR) de facturation permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale de l’ouvrant droit (assuré).</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.id</t>
+    <t>Patient.identifier:NSS-NIR.id</t>
   </si>
   <si>
     <t>Patient.identifier.id</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.extension</t>
+    <t>Patient.identifier:NSS-NIR.extension</t>
   </si>
   <si>
     <t>Patient.identifier.extension</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.use</t>
+    <t>Patient.identifier:NSS-NIR.use</t>
   </si>
   <si>
     <t>Patient.identifier.use</t>
@@ -1380,7 +1380,7 @@
     <t>Role.code or implied by context</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.type</t>
+    <t>Patient.identifier:NSS-NIR.type</t>
   </si>
   <si>
     <t>Patient.identifier.type</t>
@@ -1419,13 +1419,13 @@
     <t>CX.5</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.system</t>
+    <t>Patient.identifier:NSS-NIR.system</t>
   </si>
   <si>
     <t>Patient.identifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
+    <t>Autorité d’affectation du NIR utilisé en tant que numéro de sécurité sociale</t>
   </si>
   <si>
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
@@ -1452,7 +1452,7 @@
     <t>CX.4 / EI-2-4</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.value</t>
+    <t>Patient.identifier:NSS-NIR.value</t>
   </si>
   <si>
     <t>Patient.identifier.value</t>
@@ -1479,7 +1479,7 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.period</t>
+    <t>Patient.identifier:NSS-NIR.period</t>
   </si>
   <si>
     <t>Patient.identifier.period</t>
@@ -1500,7 +1500,7 @@
     <t>CX.7 + CX.8</t>
   </si>
   <si>
-    <t>Patient.identifier:NSS.assigner</t>
+    <t>Patient.identifier:NSS-NIR.assigner</t>
   </si>
   <si>
     <t>Patient.identifier.assigner</t>
@@ -1526,6 +1526,45 @@
   </si>
   <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA</t>
+  </si>
+  <si>
+    <t>NSS-NIA</t>
+  </si>
+  <si>
+    <t>National Health Plan Identifier | Le Numéro d'Inscription au Répertoire (NIA) de facturation d'attente permet de faire transiter le numéro de sécurité social de l’ayant droit ou du bénéfiaire (patient) / le numéro de sécurité sociale d'attente de l’ouvrant droit (assuré).</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.id</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.extension</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.use</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.type</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.system</t>
+  </si>
+  <si>
+    <t>Autorité d’affectation du NIA utilisé en tant que numéro de sécurité sociale</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.250.1.213.1.4.14</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.value</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.period</t>
+  </si>
+  <si>
+    <t>Patient.identifier:NSS-NIA.assigner</t>
   </si>
   <si>
     <t>Patient.identifier:INS-C</t>
@@ -1562,6 +1601,9 @@
   </si>
   <si>
     <t>Patient.identifier:INS-C.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
   </si>
   <si>
     <t>urn:oid:1.2.250.1.213.1.4.2</t>
@@ -3196,7 +3238,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO214"/>
+  <dimension ref="A1:AO223"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.65625" customWidth="true" bestFit="true"/>
@@ -12805,7 +12847,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -13188,7 +13230,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>490</v>
+        <v>432</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -13259,7 +13301,7 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>438</v>
@@ -13307,7 +13349,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>492</v>
+        <v>444</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>82</v>
@@ -13376,7 +13418,7 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>449</v>
@@ -13405,7 +13447,7 @@
         <v>132</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>450</v>
+        <v>492</v>
       </c>
       <c r="M88" t="s" s="2">
         <v>451</v>
@@ -13424,7 +13466,7 @@
         <v>82</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>455</v>
@@ -13495,7 +13537,7 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>460</v>
@@ -13612,7 +13654,7 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
         <v>469</v>
@@ -13727,7 +13769,7 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B91" t="s" s="2">
         <v>476</v>
@@ -13844,13 +13886,13 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B92" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D92" t="s" s="2">
         <v>82</v>
@@ -13860,7 +13902,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13875,7 +13917,7 @@
         <v>409</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>411</v>
@@ -13963,7 +14005,7 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>423</v>
@@ -14078,7 +14120,7 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B94" t="s" s="2">
         <v>425</v>
@@ -14195,7 +14237,7 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B95" t="s" s="2">
         <v>427</v>
@@ -14243,7 +14285,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -14460,7 +14502,7 @@
         <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="M97" t="s" s="2">
         <v>451</v>
@@ -14479,7 +14521,7 @@
         <v>82</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>455</v>
@@ -14550,7 +14592,7 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>460</v>
@@ -14667,7 +14709,7 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B99" t="s" s="2">
         <v>469</v>
@@ -14782,7 +14824,7 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>476</v>
@@ -14899,13 +14941,13 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>82</v>
@@ -14915,7 +14957,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14930,7 +14972,7 @@
         <v>409</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>411</v>
@@ -15018,7 +15060,7 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
         <v>423</v>
@@ -15133,7 +15175,7 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>425</v>
@@ -15250,7 +15292,7 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>427</v>
@@ -15285,7 +15327,7 @@
         <v>429</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>517</v>
+        <v>430</v>
       </c>
       <c r="O104" t="s" s="2">
         <v>431</v>
@@ -15298,7 +15340,7 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>82</v>
@@ -15315,9 +15357,11 @@
       <c r="X104" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y104" s="2"/>
+      <c r="Y104" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>518</v>
+        <v>434</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15367,7 +15411,7 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>438</v>
@@ -15415,7 +15459,7 @@
         <v>82</v>
       </c>
       <c r="S105" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="T105" t="s" s="2">
         <v>82</v>
@@ -15484,7 +15528,7 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>449</v>
@@ -15513,7 +15557,7 @@
         <v>132</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="M106" t="s" s="2">
         <v>451</v>
@@ -15532,7 +15576,7 @@
         <v>82</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>82</v>
+        <v>521</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>455</v>
@@ -16338,7 +16382,7 @@
         <v>429</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>430</v>
+        <v>531</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>431</v>
@@ -16351,7 +16395,7 @@
         <v>82</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>82</v>
@@ -16368,11 +16412,9 @@
       <c r="X113" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y113" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="Y113" s="2"/>
       <c r="Z113" t="s" s="2">
-        <v>434</v>
+        <v>532</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16422,7 +16464,7 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>438</v>
@@ -16470,7 +16512,7 @@
         <v>82</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>82</v>
@@ -16539,7 +16581,7 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>449</v>
@@ -16568,7 +16610,7 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>450</v>
+        <v>507</v>
       </c>
       <c r="M115" t="s" s="2">
         <v>451</v>
@@ -16658,7 +16700,7 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B116" t="s" s="2">
         <v>460</v>
@@ -16775,7 +16817,7 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>469</v>
@@ -16890,7 +16932,7 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B118" t="s" s="2">
         <v>476</v>
@@ -17005,15 +17047,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>82</v>
@@ -17026,7 +17068,7 @@
         <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>82</v>
@@ -17038,7 +17080,7 @@
         <v>409</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>411</v>
@@ -17126,7 +17168,7 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>423</v>
@@ -17241,7 +17283,7 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>425</v>
@@ -17358,7 +17400,7 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>427</v>
@@ -17387,13 +17429,13 @@
         <v>173</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>543</v>
+        <v>428</v>
       </c>
       <c r="M122" t="s" s="2">
         <v>429</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>544</v>
+        <v>430</v>
       </c>
       <c r="O122" t="s" s="2">
         <v>431</v>
@@ -17406,7 +17448,7 @@
         <v>82</v>
       </c>
       <c r="S122" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="T122" t="s" s="2">
         <v>82</v>
@@ -17423,9 +17465,11 @@
       <c r="X122" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y122" s="2"/>
+      <c r="Y122" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>545</v>
+        <v>434</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>82</v>
@@ -17475,7 +17519,7 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B123" t="s" s="2">
         <v>438</v>
@@ -17523,7 +17567,7 @@
         <v>82</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>82</v>
@@ -17540,11 +17584,9 @@
       <c r="X123" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Y123" t="s" s="2">
-        <v>548</v>
-      </c>
+      <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>549</v>
+        <v>445</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>82</v>
@@ -17594,7 +17636,7 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B124" t="s" s="2">
         <v>449</v>
@@ -17623,7 +17665,7 @@
         <v>132</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>551</v>
+        <v>507</v>
       </c>
       <c r="M124" t="s" s="2">
         <v>451</v>
@@ -17642,7 +17684,7 @@
         <v>82</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>455</v>
@@ -17713,7 +17755,7 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>460</v>
@@ -17830,7 +17872,7 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>469</v>
@@ -17945,7 +17987,7 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>476</v>
@@ -18060,15 +18102,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B128" t="s" s="2">
         <v>408</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>82</v>
@@ -18081,7 +18123,7 @@
         <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>82</v>
@@ -18093,7 +18135,7 @@
         <v>409</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="M128" t="s" s="2">
         <v>411</v>
@@ -18181,7 +18223,7 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B129" t="s" s="2">
         <v>423</v>
@@ -18296,7 +18338,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>425</v>
@@ -18413,7 +18455,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>427</v>
@@ -18442,13 +18484,13 @@
         <v>173</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>428</v>
+        <v>557</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>429</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>430</v>
+        <v>558</v>
       </c>
       <c r="O131" t="s" s="2">
         <v>431</v>
@@ -18461,7 +18503,7 @@
         <v>82</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>82</v>
@@ -18478,11 +18520,9 @@
       <c r="X131" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y131" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="Y131" s="2"/>
       <c r="Z131" t="s" s="2">
-        <v>434</v>
+        <v>559</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>82</v>
@@ -18532,7 +18572,7 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>438</v>
@@ -18580,7 +18620,7 @@
         <v>82</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>82</v>
@@ -18598,10 +18638,10 @@
         <v>155</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>82</v>
@@ -19655,10 +19695,10 @@
         <v>155</v>
       </c>
       <c r="Y141" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="Z141" t="s" s="2">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>82</v>
@@ -20174,7 +20214,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
         <v>584</v>
       </c>
@@ -20195,7 +20235,7 @@
         <v>81</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>82</v>
@@ -20556,13 +20596,13 @@
         <v>173</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>543</v>
+        <v>428</v>
       </c>
       <c r="M149" t="s" s="2">
         <v>429</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>590</v>
+        <v>430</v>
       </c>
       <c r="O149" t="s" s="2">
         <v>431</v>
@@ -20575,7 +20615,7 @@
         <v>82</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>82</v>
@@ -20592,9 +20632,11 @@
       <c r="X149" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Y149" s="2"/>
+      <c r="Y149" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>545</v>
+        <v>434</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>82</v>
@@ -20644,7 +20686,7 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>438</v>
@@ -20692,7 +20734,7 @@
         <v>82</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>82</v>
@@ -20710,10 +20752,10 @@
         <v>155</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>82</v>
@@ -20763,7 +20805,7 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>449</v>
@@ -20792,7 +20834,7 @@
         <v>132</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>451</v>
@@ -20811,7 +20853,7 @@
         <v>82</v>
       </c>
       <c r="S151" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="T151" t="s" s="2">
         <v>455</v>
@@ -20882,7 +20924,7 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>460</v>
@@ -20999,7 +21041,7 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>469</v>
@@ -21114,7 +21156,7 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>476</v>
@@ -21229,14 +21271,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="C155" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="B155" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21245,38 +21289,34 @@
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J155" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K155" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L155" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="L155" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="M155" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>603</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" t="s" s="2">
-        <v>604</v>
+        <v>412</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q155" t="s" s="2">
-        <v>605</v>
-      </c>
+      <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
         <v>82</v>
       </c>
@@ -21320,13 +21360,13 @@
         <v>82</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>599</v>
+        <v>408</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH155" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI155" t="s" s="2">
         <v>82</v>
@@ -21335,16 +21375,16 @@
         <v>102</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>606</v>
+        <v>415</v>
       </c>
       <c r="AL155" t="s" s="2">
-        <v>108</v>
+        <v>416</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>607</v>
+        <v>417</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>82</v>
@@ -21352,10 +21392,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>608</v>
+        <v>423</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21363,10 +21403,10 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>82</v>
@@ -21375,23 +21415,19 @@
         <v>82</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>609</v>
+        <v>104</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>610</v>
+        <v>105</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N156" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O156" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
         <v>82</v>
       </c>
@@ -21427,41 +21463,43 @@
         <v>82</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AC156" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>608</v>
+        <v>107</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK156" t="s" s="2">
-        <v>615</v>
+        <v>108</v>
       </c>
       <c r="AL156" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AM156" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>82</v>
@@ -21469,16 +21507,14 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C157" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -21494,23 +21530,21 @@
         <v>82</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>620</v>
+        <v>111</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>621</v>
+        <v>112</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>622</v>
+        <v>113</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>82</v>
       </c>
@@ -21546,19 +21580,19 @@
         <v>82</v>
       </c>
       <c r="AB157" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE157" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>608</v>
+        <v>118</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -21570,19 +21604,19 @@
         <v>82</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK157" t="s" s="2">
-        <v>615</v>
+        <v>108</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AM157" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>82</v>
@@ -21590,10 +21624,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>624</v>
+        <v>427</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21601,7 +21635,7 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G158" t="s" s="2">
         <v>90</v>
@@ -21610,22 +21644,26 @@
         <v>82</v>
       </c>
       <c r="I158" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>104</v>
+        <v>173</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>105</v>
+        <v>557</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N158" s="2"/>
-      <c r="O158" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P158" t="s" s="2">
         <v>82</v>
       </c>
@@ -21649,13 +21687,11 @@
         <v>82</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y158" s="2"/>
       <c r="Z158" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>82</v>
@@ -21673,7 +21709,7 @@
         <v>82</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>107</v>
+        <v>435</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -21685,10 +21721,10 @@
         <v>82</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK158" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="AL158" t="s" s="2">
         <v>82</v>
@@ -21697,7 +21733,7 @@
         <v>82</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>82</v>
@@ -21705,21 +21741,21 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>625</v>
+        <v>605</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>626</v>
+        <v>438</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E159" s="2"/>
       <c r="F159" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>82</v>
@@ -21728,21 +21764,23 @@
         <v>82</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>111</v>
+        <v>439</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>112</v>
+        <v>440</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>113</v>
+        <v>441</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O159" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O159" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P159" t="s" s="2">
         <v>82</v>
       </c>
@@ -21751,7 +21789,7 @@
         <v>82</v>
       </c>
       <c r="S159" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="T159" t="s" s="2">
         <v>82</v>
@@ -21766,46 +21804,46 @@
         <v>82</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>118</v>
+        <v>446</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>108</v>
+        <v>436</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>82</v>
@@ -21814,7 +21852,7 @@
         <v>82</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>82</v>
@@ -21822,10 +21860,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>628</v>
+        <v>449</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21842,25 +21880,25 @@
         <v>82</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J160" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>630</v>
+        <v>451</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>631</v>
+        <v>452</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>632</v>
+        <v>453</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>82</v>
@@ -21870,10 +21908,10 @@
         <v>82</v>
       </c>
       <c r="S160" t="s" s="2">
-        <v>633</v>
+        <v>609</v>
       </c>
       <c r="T160" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="U160" t="s" s="2">
         <v>82</v>
@@ -21885,13 +21923,13 @@
         <v>82</v>
       </c>
       <c r="X160" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y160" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="Z160" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AA160" t="s" s="2">
         <v>82</v>
@@ -21909,7 +21947,7 @@
         <v>82</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>636</v>
+        <v>456</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -21924,7 +21962,7 @@
         <v>102</v>
       </c>
       <c r="AK160" t="s" s="2">
-        <v>314</v>
+        <v>457</v>
       </c>
       <c r="AL160" t="s" s="2">
         <v>82</v>
@@ -21933,7 +21971,7 @@
         <v>82</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>637</v>
+        <v>458</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>82</v>
@@ -21941,10 +21979,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>639</v>
+        <v>460</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21952,7 +21990,7 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G161" t="s" s="2">
         <v>90</v>
@@ -21970,17 +22008,15 @@
         <v>104</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>640</v>
+        <v>461</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>641</v>
+        <v>462</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>463</v>
+      </c>
+      <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
         <v>82</v>
       </c>
@@ -21992,7 +22028,7 @@
         <v>82</v>
       </c>
       <c r="T161" t="s" s="2">
-        <v>82</v>
+        <v>464</v>
       </c>
       <c r="U161" t="s" s="2">
         <v>82</v>
@@ -22028,7 +22064,7 @@
         <v>82</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>643</v>
+        <v>465</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -22043,7 +22079,7 @@
         <v>102</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>334</v>
+        <v>466</v>
       </c>
       <c r="AL161" t="s" s="2">
         <v>82</v>
@@ -22052,7 +22088,7 @@
         <v>82</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>644</v>
+        <v>467</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>82</v>
@@ -22060,14 +22096,14 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>645</v>
+        <v>611</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>646</v>
+        <v>469</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
@@ -22086,17 +22122,15 @@
         <v>91</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>648</v>
+        <v>470</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>650</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
         <v>82</v>
@@ -22145,7 +22179,7 @@
         <v>82</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>651</v>
+        <v>472</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -22160,7 +22194,7 @@
         <v>102</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>652</v>
+        <v>473</v>
       </c>
       <c r="AL162" t="s" s="2">
         <v>82</v>
@@ -22169,7 +22203,7 @@
         <v>82</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>653</v>
+        <v>474</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>82</v>
@@ -22177,21 +22211,21 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>654</v>
+        <v>612</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>655</v>
+        <v>476</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>82</v>
@@ -22203,16 +22237,16 @@
         <v>91</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>104</v>
+        <v>477</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>657</v>
+        <v>478</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>658</v>
+        <v>479</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>659</v>
+        <v>480</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -22262,13 +22296,13 @@
         <v>82</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>660</v>
+        <v>481</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH163" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI163" t="s" s="2">
         <v>82</v>
@@ -22277,7 +22311,7 @@
         <v>102</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>661</v>
+        <v>482</v>
       </c>
       <c r="AL163" t="s" s="2">
         <v>82</v>
@@ -22286,7 +22320,7 @@
         <v>82</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>662</v>
+        <v>483</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>82</v>
@@ -22294,10 +22328,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>663</v>
+        <v>613</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>664</v>
+        <v>613</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22308,32 +22342,38 @@
         <v>80</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I164" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J164" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>104</v>
+        <v>614</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>665</v>
+        <v>615</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q164" s="2"/>
+      <c r="Q164" t="s" s="2">
+        <v>619</v>
+      </c>
       <c r="R164" t="s" s="2">
         <v>82</v>
       </c>
@@ -22377,13 +22417,13 @@
         <v>82</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>667</v>
+        <v>613</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>82</v>
@@ -22392,16 +22432,16 @@
         <v>102</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>668</v>
+        <v>620</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AO164" t="s" s="2">
         <v>82</v>
@@ -22409,10 +22449,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>670</v>
+        <v>622</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>671</v>
+        <v>622</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22420,7 +22460,7 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>81</v>
@@ -22435,16 +22475,20 @@
         <v>91</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>104</v>
+        <v>623</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>672</v>
+        <v>624</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N165" s="2"/>
-      <c r="O165" s="2"/>
+        <v>625</v>
+      </c>
+      <c r="N165" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O165" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P165" t="s" s="2">
         <v>82</v>
       </c>
@@ -22480,19 +22524,17 @@
         <v>82</v>
       </c>
       <c r="AB165" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC165" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="AC165" s="2"/>
       <c r="AD165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE165" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>674</v>
+        <v>622</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -22507,16 +22549,16 @@
         <v>102</v>
       </c>
       <c r="AK165" t="s" s="2">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="AL165" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AM165" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>676</v>
+        <v>631</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>82</v>
@@ -22524,12 +22566,14 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>677</v>
+        <v>632</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="C166" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="C166" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="D166" t="s" s="2">
         <v>82</v>
       </c>
@@ -22538,7 +22582,7 @@
         <v>80</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>82</v>
@@ -22550,17 +22594,19 @@
         <v>91</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>390</v>
+        <v>634</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>679</v>
+        <v>635</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N166" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="N166" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="O166" t="s" s="2">
-        <v>681</v>
+        <v>627</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>82</v>
@@ -22609,13 +22655,13 @@
         <v>82</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>682</v>
+        <v>622</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>82</v>
@@ -22624,65 +22670,59 @@
         <v>102</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>396</v>
+        <v>629</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AM166" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>683</v>
+        <v>631</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>684</v>
+        <v>637</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C167" t="s" s="2">
-        <v>685</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>620</v>
+        <v>104</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>686</v>
+        <v>105</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>613</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>82</v>
       </c>
@@ -22730,31 +22770,31 @@
         <v>82</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>608</v>
+        <v>107</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH167" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK167" t="s" s="2">
-        <v>615</v>
+        <v>108</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>616</v>
+        <v>82</v>
       </c>
       <c r="AM167" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>617</v>
+        <v>82</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>82</v>
@@ -22762,21 +22802,21 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>688</v>
+        <v>639</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>624</v>
+        <v>640</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E168" s="2"/>
       <c r="F168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H168" t="s" s="2">
         <v>82</v>
@@ -22788,15 +22828,17 @@
         <v>82</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N168" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N168" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>82</v>
@@ -22833,31 +22875,31 @@
         <v>82</v>
       </c>
       <c r="AB168" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC168" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE168" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH168" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI168" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>108</v>
@@ -22877,10 +22919,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>689</v>
+        <v>641</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>626</v>
+        <v>642</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -22891,28 +22933,32 @@
         <v>90</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I169" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>198</v>
+        <v>643</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N169" s="2"/>
-      <c r="O169" s="2"/>
+        <v>644</v>
+      </c>
+      <c r="N169" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P169" t="s" s="2">
         <v>82</v>
       </c>
@@ -22921,7 +22967,7 @@
         <v>82</v>
       </c>
       <c r="S169" t="s" s="2">
-        <v>82</v>
+        <v>647</v>
       </c>
       <c r="T169" t="s" s="2">
         <v>82</v>
@@ -22936,46 +22982,46 @@
         <v>82</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y169" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="Z169" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>118</v>
+        <v>650</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="AL169" t="s" s="2">
         <v>82</v>
@@ -22984,52 +23030,54 @@
         <v>82</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>82</v>
+        <v>651</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>690</v>
+        <v>652</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C170" t="s" s="2">
-        <v>691</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J170" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I170" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J170" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K170" t="s" s="2">
-        <v>692</v>
+        <v>104</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>693</v>
+        <v>654</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O170" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="P170" t="s" s="2">
         <v>82</v>
       </c>
@@ -23077,22 +23125,22 @@
         <v>82</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>118</v>
+        <v>657</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AL170" t="s" s="2">
         <v>82</v>
@@ -23101,7 +23149,7 @@
         <v>82</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>82</v>
+        <v>658</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>82</v>
@@ -23109,18 +23157,18 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>695</v>
+        <v>659</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>628</v>
+        <v>660</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
         <v>90</v>
@@ -23129,26 +23177,24 @@
         <v>82</v>
       </c>
       <c r="I171" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J171" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>173</v>
+        <v>104</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>629</v>
+        <v>662</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>630</v>
+        <v>663</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="O171" t="s" s="2">
-        <v>632</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
         <v>82</v>
       </c>
@@ -23157,7 +23203,7 @@
         <v>82</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>432</v>
+        <v>82</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>82</v>
@@ -23172,13 +23218,13 @@
         <v>82</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y171" t="s" s="2">
-        <v>634</v>
+        <v>82</v>
       </c>
       <c r="Z171" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>82</v>
@@ -23196,7 +23242,7 @@
         <v>82</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>636</v>
+        <v>665</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
@@ -23211,7 +23257,7 @@
         <v>102</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>314</v>
+        <v>666</v>
       </c>
       <c r="AL171" t="s" s="2">
         <v>82</v>
@@ -23220,7 +23266,7 @@
         <v>82</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>637</v>
+        <v>667</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>82</v>
@@ -23228,21 +23274,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>696</v>
+        <v>668</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>639</v>
+        <v>669</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
-        <v>82</v>
+        <v>670</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>82</v>
@@ -23257,17 +23303,15 @@
         <v>104</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>640</v>
+        <v>671</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>641</v>
+        <v>672</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O172" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>673</v>
+      </c>
+      <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
         <v>82</v>
       </c>
@@ -23315,13 +23359,13 @@
         <v>82</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>643</v>
+        <v>674</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>82</v>
@@ -23330,7 +23374,7 @@
         <v>102</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>334</v>
+        <v>675</v>
       </c>
       <c r="AL172" t="s" s="2">
         <v>82</v>
@@ -23339,7 +23383,7 @@
         <v>82</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>644</v>
+        <v>676</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>82</v>
@@ -23347,21 +23391,21 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>646</v>
+        <v>678</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
-        <v>647</v>
+        <v>82</v>
       </c>
       <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>82</v>
@@ -23376,14 +23420,12 @@
         <v>104</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>648</v>
+        <v>679</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="N173" t="s" s="2">
-        <v>650</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="N173" s="2"/>
       <c r="O173" s="2"/>
       <c r="P173" t="s" s="2">
         <v>82</v>
@@ -23432,13 +23474,13 @@
         <v>82</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH173" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI173" t="s" s="2">
         <v>82</v>
@@ -23447,7 +23489,7 @@
         <v>102</v>
       </c>
       <c r="AK173" t="s" s="2">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="AL173" t="s" s="2">
         <v>82</v>
@@ -23456,7 +23498,7 @@
         <v>82</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>82</v>
@@ -23464,21 +23506,21 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
-        <v>656</v>
+        <v>82</v>
       </c>
       <c r="E174" s="2"/>
       <c r="F174" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>82</v>
@@ -23493,14 +23535,12 @@
         <v>104</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>659</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="N174" s="2"/>
       <c r="O174" s="2"/>
       <c r="P174" t="s" s="2">
         <v>82</v>
@@ -23549,7 +23589,7 @@
         <v>82</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>660</v>
+        <v>688</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -23564,7 +23604,7 @@
         <v>102</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>661</v>
+        <v>689</v>
       </c>
       <c r="AL174" t="s" s="2">
         <v>82</v>
@@ -23573,7 +23613,7 @@
         <v>82</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>662</v>
+        <v>690</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>82</v>
@@ -23581,10 +23621,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>664</v>
+        <v>692</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23595,7 +23635,7 @@
         <v>80</v>
       </c>
       <c r="G175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H175" t="s" s="2">
         <v>82</v>
@@ -23607,16 +23647,18 @@
         <v>91</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>104</v>
+        <v>390</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>665</v>
+        <v>693</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>666</v>
+        <v>694</v>
       </c>
       <c r="N175" s="2"/>
-      <c r="O175" s="2"/>
+      <c r="O175" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P175" t="s" s="2">
         <v>82</v>
       </c>
@@ -23664,13 +23706,13 @@
         <v>82</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>667</v>
+        <v>696</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH175" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI175" t="s" s="2">
         <v>82</v>
@@ -23679,7 +23721,7 @@
         <v>102</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>668</v>
+        <v>396</v>
       </c>
       <c r="AL175" t="s" s="2">
         <v>82</v>
@@ -23688,32 +23730,34 @@
         <v>82</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="C176" s="2"/>
+        <v>622</v>
+      </c>
+      <c r="C176" t="s" s="2">
+        <v>699</v>
+      </c>
       <c r="D176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>82</v>
@@ -23722,16 +23766,20 @@
         <v>91</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>104</v>
+        <v>634</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>672</v>
+        <v>700</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="N176" s="2"/>
-      <c r="O176" s="2"/>
+        <v>701</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P176" t="s" s="2">
         <v>82</v>
       </c>
@@ -23779,7 +23827,7 @@
         <v>82</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>674</v>
+        <v>622</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -23794,16 +23842,16 @@
         <v>102</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>675</v>
+        <v>629</v>
       </c>
       <c r="AL176" t="s" s="2">
-        <v>82</v>
+        <v>630</v>
       </c>
       <c r="AM176" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>676</v>
+        <v>631</v>
       </c>
       <c r="AO176" t="s" s="2">
         <v>82</v>
@@ -23814,7 +23862,7 @@
         <v>702</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23834,21 +23882,19 @@
         <v>82</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>390</v>
+        <v>104</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>679</v>
+        <v>105</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>680</v>
+        <v>106</v>
       </c>
       <c r="N177" s="2"/>
-      <c r="O177" t="s" s="2">
-        <v>681</v>
-      </c>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>82</v>
       </c>
@@ -23896,7 +23942,7 @@
         <v>82</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>682</v>
+        <v>107</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -23908,10 +23954,10 @@
         <v>82</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>396</v>
+        <v>108</v>
       </c>
       <c r="AL177" t="s" s="2">
         <v>82</v>
@@ -23920,7 +23966,7 @@
         <v>82</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>683</v>
+        <v>82</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>82</v>
@@ -23931,7 +23977,7 @@
         <v>703</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>703</v>
+        <v>640</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23939,7 +23985,7 @@
       </c>
       <c r="E178" s="2"/>
       <c r="F178" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G178" t="s" s="2">
         <v>81</v>
@@ -23951,23 +23997,19 @@
         <v>82</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>704</v>
+        <v>111</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>705</v>
+        <v>198</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>82</v>
       </c>
@@ -24003,19 +24045,19 @@
         <v>82</v>
       </c>
       <c r="AB178" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE178" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>703</v>
+        <v>118</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -24027,19 +24069,19 @@
         <v>82</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>709</v>
+        <v>82</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>710</v>
+        <v>82</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>711</v>
+        <v>82</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>82</v>
@@ -24047,12 +24089,14 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="C179" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="C179" t="s" s="2">
+        <v>705</v>
+      </c>
       <c r="D179" t="s" s="2">
         <v>82</v>
       </c>
@@ -24070,23 +24114,19 @@
         <v>82</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>173</v>
+        <v>706</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>716</v>
-      </c>
+        <v>708</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>82</v>
       </c>
@@ -24110,11 +24150,13 @@
         <v>82</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="Y179" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z179" t="s" s="2">
-        <v>717</v>
+        <v>82</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>82</v>
@@ -24132,42 +24174,42 @@
         <v>82</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>712</v>
+        <v>118</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>718</v>
+        <v>82</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>719</v>
+        <v>82</v>
       </c>
       <c r="AM179" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>720</v>
+        <v>82</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>721</v>
+        <v>642</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24181,28 +24223,28 @@
         <v>90</v>
       </c>
       <c r="H180" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I180" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I180" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J180" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>722</v>
+        <v>643</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>723</v>
+        <v>644</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>724</v>
+        <v>645</v>
       </c>
       <c r="O180" t="s" s="2">
-        <v>725</v>
+        <v>646</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>82</v>
@@ -24212,7 +24254,7 @@
         <v>82</v>
       </c>
       <c r="S180" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="T180" t="s" s="2">
         <v>82</v>
@@ -24227,13 +24269,13 @@
         <v>82</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>82</v>
+        <v>648</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>82</v>
@@ -24251,7 +24293,7 @@
         <v>82</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>721</v>
+        <v>650</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -24266,27 +24308,27 @@
         <v>102</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>726</v>
+        <v>314</v>
       </c>
       <c r="AL180" t="s" s="2">
-        <v>727</v>
+        <v>82</v>
       </c>
       <c r="AM180" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>728</v>
+        <v>651</v>
       </c>
       <c r="AO180" t="s" s="2">
-        <v>729</v>
+        <v>82</v>
       </c>
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>730</v>
+        <v>710</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>730</v>
+        <v>653</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24303,25 +24345,25 @@
         <v>82</v>
       </c>
       <c r="I181" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J181" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>731</v>
+        <v>104</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>732</v>
+        <v>654</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>733</v>
+        <v>655</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>734</v>
+        <v>656</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>735</v>
+        <v>331</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>82</v>
@@ -24370,7 +24412,7 @@
         <v>82</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>730</v>
+        <v>657</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -24385,16 +24427,16 @@
         <v>102</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>736</v>
+        <v>334</v>
       </c>
       <c r="AL181" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM181" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>737</v>
+        <v>658</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>82</v>
@@ -24402,21 +24444,21 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>738</v>
+        <v>711</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>738</v>
+        <v>660</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
-        <v>82</v>
+        <v>661</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>82</v>
@@ -24428,20 +24470,18 @@
         <v>91</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>292</v>
+        <v>104</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>739</v>
+        <v>662</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>740</v>
+        <v>663</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="O182" t="s" s="2">
-        <v>742</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
         <v>82</v>
       </c>
@@ -24489,13 +24529,13 @@
         <v>82</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>738</v>
+        <v>665</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH182" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI182" t="s" s="2">
         <v>82</v>
@@ -24504,16 +24544,16 @@
         <v>102</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>744</v>
+        <v>82</v>
       </c>
       <c r="AM182" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>745</v>
+        <v>667</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>82</v>
@@ -24521,18 +24561,18 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>746</v>
+        <v>712</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>746</v>
+        <v>669</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
-        <v>82</v>
+        <v>670</v>
       </c>
       <c r="E183" s="2"/>
       <c r="F183" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G183" t="s" s="2">
         <v>90</v>
@@ -24544,21 +24584,21 @@
         <v>82</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>439</v>
+        <v>104</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>747</v>
+        <v>713</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" t="s" s="2">
-        <v>749</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
         <v>82</v>
       </c>
@@ -24582,11 +24622,13 @@
         <v>82</v>
       </c>
       <c r="X183" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y183" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z183" t="s" s="2">
-        <v>750</v>
+        <v>82</v>
       </c>
       <c r="AA183" t="s" s="2">
         <v>82</v>
@@ -24604,13 +24646,13 @@
         <v>82</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>746</v>
+        <v>674</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH183" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI183" t="s" s="2">
         <v>82</v>
@@ -24619,16 +24661,16 @@
         <v>102</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>751</v>
+        <v>675</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>752</v>
+        <v>82</v>
       </c>
       <c r="AM183" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>753</v>
+        <v>676</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>82</v>
@@ -24636,10 +24678,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>754</v>
+        <v>714</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>754</v>
+        <v>678</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24650,7 +24692,7 @@
         <v>80</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>82</v>
@@ -24659,23 +24701,19 @@
         <v>82</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>755</v>
+        <v>104</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>756</v>
+        <v>679</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>759</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="N184" s="2"/>
+      <c r="O184" s="2"/>
       <c r="P184" t="s" s="2">
         <v>82</v>
       </c>
@@ -24723,13 +24761,13 @@
         <v>82</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>754</v>
+        <v>681</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI184" t="s" s="2">
         <v>82</v>
@@ -24738,16 +24776,16 @@
         <v>102</v>
       </c>
       <c r="AK184" t="s" s="2">
-        <v>760</v>
+        <v>682</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM184" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>761</v>
+        <v>683</v>
       </c>
       <c r="AO184" t="s" s="2">
         <v>82</v>
@@ -24755,10 +24793,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>762</v>
+        <v>715</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>762</v>
+        <v>685</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24778,23 +24816,19 @@
         <v>82</v>
       </c>
       <c r="J185" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>763</v>
+        <v>104</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>764</v>
+        <v>686</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>767</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="N185" s="2"/>
+      <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>82</v>
       </c>
@@ -24842,7 +24876,7 @@
         <v>82</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>762</v>
+        <v>688</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -24857,16 +24891,16 @@
         <v>102</v>
       </c>
       <c r="AK185" t="s" s="2">
-        <v>768</v>
+        <v>689</v>
       </c>
       <c r="AL185" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM185" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN185" t="s" s="2">
-        <v>769</v>
+        <v>690</v>
       </c>
       <c r="AO185" t="s" s="2">
         <v>82</v>
@@ -24874,10 +24908,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>770</v>
+        <v>716</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>770</v>
+        <v>692</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24888,7 +24922,7 @@
         <v>80</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>82</v>
@@ -24897,22 +24931,20 @@
         <v>82</v>
       </c>
       <c r="J186" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>771</v>
+        <v>390</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>772</v>
+        <v>693</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="N186" t="s" s="2">
-        <v>774</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>775</v>
+        <v>695</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>82</v>
@@ -24961,31 +24993,31 @@
         <v>82</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>770</v>
+        <v>696</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>776</v>
+        <v>102</v>
       </c>
       <c r="AK186" t="s" s="2">
-        <v>777</v>
+        <v>396</v>
       </c>
       <c r="AL186" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM186" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN186" t="s" s="2">
-        <v>82</v>
+        <v>697</v>
       </c>
       <c r="AO186" t="s" s="2">
         <v>82</v>
@@ -24993,10 +25025,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>778</v>
+        <v>717</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>778</v>
+        <v>717</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -25007,7 +25039,7 @@
         <v>80</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>82</v>
@@ -25016,19 +25048,23 @@
         <v>82</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>104</v>
+        <v>718</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>105</v>
+        <v>719</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N187" s="2"/>
-      <c r="O187" s="2"/>
+        <v>720</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>721</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="P187" t="s" s="2">
         <v>82</v>
       </c>
@@ -25076,42 +25112,42 @@
         <v>82</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>107</v>
+        <v>717</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH187" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK187" t="s" s="2">
-        <v>108</v>
+        <v>723</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>82</v>
+        <v>724</v>
       </c>
       <c r="AM187" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN187" t="s" s="2">
-        <v>82</v>
+        <v>725</v>
       </c>
       <c r="AO187" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="188" hidden="true">
+    <row r="188">
       <c r="A188" t="s" s="2">
-        <v>779</v>
+        <v>726</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>779</v>
+        <v>726</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25119,31 +25155,35 @@
       </c>
       <c r="E188" s="2"/>
       <c r="F188" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G188" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>198</v>
+        <v>727</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N188" s="2"/>
-      <c r="O188" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>730</v>
+      </c>
       <c r="P188" t="s" s="2">
         <v>82</v>
       </c>
@@ -25167,98 +25207,100 @@
         <v>82</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y188" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="Y188" s="2"/>
       <c r="Z188" t="s" s="2">
-        <v>82</v>
+        <v>731</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AC188" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE188" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>118</v>
+        <v>726</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH188" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>82</v>
+        <v>732</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>82</v>
+        <v>733</v>
       </c>
       <c r="AM188" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN188" t="s" s="2">
-        <v>82</v>
+        <v>734</v>
       </c>
       <c r="AO188" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="189" hidden="true">
+    <row r="189">
       <c r="A189" t="s" s="2">
-        <v>780</v>
+        <v>735</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="C189" t="s" s="2">
-        <v>781</v>
-      </c>
+        <v>735</v>
+      </c>
+      <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E189" s="2"/>
       <c r="F189" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G189" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>782</v>
+        <v>242</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>783</v>
+        <v>736</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+        <v>737</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>738</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>739</v>
+      </c>
       <c r="P189" t="s" s="2">
         <v>82</v>
       </c>
@@ -25306,46 +25348,44 @@
         <v>82</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>118</v>
+        <v>735</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>82</v>
+        <v>740</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>82</v>
+        <v>741</v>
       </c>
       <c r="AM189" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>82</v>
+        <v>742</v>
       </c>
       <c r="AO189" t="s" s="2">
-        <v>82</v>
+        <v>743</v>
       </c>
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>785</v>
+        <v>744</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="C190" t="s" s="2">
-        <v>786</v>
-      </c>
+        <v>744</v>
+      </c>
+      <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
         <v>82</v>
       </c>
@@ -25360,22 +25400,26 @@
         <v>82</v>
       </c>
       <c r="I190" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>787</v>
+        <v>745</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>788</v>
+        <v>746</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="N190" s="2"/>
-      <c r="O190" s="2"/>
+        <v>747</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>748</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>749</v>
+      </c>
       <c r="P190" t="s" s="2">
         <v>82</v>
       </c>
@@ -25423,31 +25467,31 @@
         <v>82</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>118</v>
+        <v>744</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>82</v>
+        <v>750</v>
       </c>
       <c r="AL190" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM190" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>82</v>
+        <v>751</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>82</v>
@@ -25455,14 +25499,14 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>790</v>
+        <v>752</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>790</v>
+        <v>752</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
-        <v>791</v>
+        <v>82</v>
       </c>
       <c r="E191" s="2"/>
       <c r="F191" t="s" s="2">
@@ -25475,25 +25519,25 @@
         <v>82</v>
       </c>
       <c r="I191" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J191" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>111</v>
+        <v>292</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>792</v>
+        <v>753</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>793</v>
+        <v>754</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>114</v>
+        <v>755</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>406</v>
+        <v>756</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>82</v>
@@ -25542,7 +25586,7 @@
         <v>82</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>794</v>
+        <v>752</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -25554,19 +25598,19 @@
         <v>82</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>196</v>
+        <v>757</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>82</v>
+        <v>758</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>82</v>
+        <v>759</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>82</v>
@@ -25574,10 +25618,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>795</v>
+        <v>760</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>795</v>
+        <v>760</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25588,7 +25632,7 @@
         <v>80</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>82</v>
@@ -25603,14 +25647,14 @@
         <v>439</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>796</v>
+        <v>761</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>797</v>
+        <v>762</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" t="s" s="2">
-        <v>798</v>
+        <v>763</v>
       </c>
       <c r="P192" t="s" s="2">
         <v>82</v>
@@ -25637,33 +25681,33 @@
       <c r="X192" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="Y192" t="s" s="2">
-        <v>799</v>
-      </c>
+      <c r="Y192" s="2"/>
       <c r="Z192" t="s" s="2">
-        <v>800</v>
+        <v>764</v>
       </c>
       <c r="AA192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB192" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC192" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE192" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>795</v>
+        <v>760</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>82</v>
@@ -25672,16 +25716,16 @@
         <v>102</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>801</v>
+        <v>765</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>108</v>
+        <v>766</v>
       </c>
       <c r="AM192" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>802</v>
+        <v>767</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>82</v>
@@ -25689,14 +25733,12 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>803</v>
+        <v>768</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="C193" t="s" s="2">
-        <v>804</v>
-      </c>
+        <v>768</v>
+      </c>
+      <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
         <v>82</v>
       </c>
@@ -25717,17 +25759,19 @@
         <v>82</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>439</v>
+        <v>769</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>805</v>
+        <v>770</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="N193" s="2"/>
+        <v>771</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>772</v>
+      </c>
       <c r="O193" t="s" s="2">
-        <v>798</v>
+        <v>773</v>
       </c>
       <c r="P193" t="s" s="2">
         <v>82</v>
@@ -25752,11 +25796,13 @@
         <v>82</v>
       </c>
       <c r="X193" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y193" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z193" t="s" s="2">
-        <v>806</v>
+        <v>82</v>
       </c>
       <c r="AA193" t="s" s="2">
         <v>82</v>
@@ -25774,13 +25820,13 @@
         <v>82</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>795</v>
+        <v>768</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI193" t="s" s="2">
         <v>82</v>
@@ -25789,7 +25835,7 @@
         <v>102</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>801</v>
+        <v>774</v>
       </c>
       <c r="AL193" t="s" s="2">
         <v>108</v>
@@ -25798,7 +25844,7 @@
         <v>82</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>802</v>
+        <v>775</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>82</v>
@@ -25806,14 +25852,12 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>807</v>
+        <v>776</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>808</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>82</v>
       </c>
@@ -25822,7 +25866,7 @@
         <v>80</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>82</v>
@@ -25834,17 +25878,19 @@
         <v>82</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>439</v>
+        <v>777</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>809</v>
+        <v>778</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="N194" s="2"/>
+        <v>779</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>780</v>
+      </c>
       <c r="O194" t="s" s="2">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>82</v>
@@ -25869,11 +25915,13 @@
         <v>82</v>
       </c>
       <c r="X194" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y194" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z194" t="s" s="2">
-        <v>810</v>
+        <v>82</v>
       </c>
       <c r="AA194" t="s" s="2">
         <v>82</v>
@@ -25891,7 +25939,7 @@
         <v>82</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
@@ -25906,7 +25954,7 @@
         <v>102</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="AL194" t="s" s="2">
         <v>108</v>
@@ -25915,7 +25963,7 @@
         <v>82</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>82</v>
@@ -25923,10 +25971,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>811</v>
+        <v>784</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>811</v>
+        <v>784</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25937,7 +25985,7 @@
         <v>80</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>82</v>
@@ -25949,17 +25997,19 @@
         <v>82</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>609</v>
+        <v>785</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>812</v>
+        <v>786</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="N195" s="2"/>
+        <v>787</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>788</v>
+      </c>
       <c r="O195" t="s" s="2">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="P195" t="s" s="2">
         <v>82</v>
@@ -26008,22 +26058,22 @@
         <v>82</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>811</v>
+        <v>784</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ195" t="s" s="2">
-        <v>102</v>
+        <v>790</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>615</v>
+        <v>791</v>
       </c>
       <c r="AL195" t="s" s="2">
         <v>108</v>
@@ -26032,7 +26082,7 @@
         <v>82</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>815</v>
+        <v>82</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>82</v>
@@ -26040,10 +26090,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>816</v>
+        <v>792</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26054,7 +26104,7 @@
         <v>80</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>82</v>
@@ -26066,20 +26116,16 @@
         <v>82</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>704</v>
+        <v>104</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>817</v>
+        <v>105</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>818</v>
-      </c>
-      <c r="N196" t="s" s="2">
-        <v>819</v>
-      </c>
-      <c r="O196" t="s" s="2">
-        <v>708</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
       <c r="P196" t="s" s="2">
         <v>82</v>
       </c>
@@ -26127,31 +26173,31 @@
         <v>82</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>816</v>
+        <v>107</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>709</v>
+        <v>108</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM196" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>820</v>
+        <v>82</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>82</v>
@@ -26159,10 +26205,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>821</v>
+        <v>793</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>821</v>
+        <v>793</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26173,7 +26219,7 @@
         <v>80</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>82</v>
@@ -26185,18 +26231,16 @@
         <v>82</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>822</v>
+        <v>111</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>823</v>
+        <v>198</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>824</v>
+        <v>199</v>
       </c>
       <c r="N197" s="2"/>
-      <c r="O197" t="s" s="2">
-        <v>825</v>
-      </c>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>82</v>
       </c>
@@ -26232,43 +26276,41 @@
         <v>82</v>
       </c>
       <c r="AB197" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC197" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC197" s="2"/>
       <c r="AD197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE197" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>821</v>
+        <v>118</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK197" t="s" s="2">
-        <v>743</v>
+        <v>82</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM197" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>826</v>
+        <v>82</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>82</v>
@@ -26276,12 +26318,14 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>827</v>
+        <v>794</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="C198" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="C198" t="s" s="2">
+        <v>795</v>
+      </c>
       <c r="D198" t="s" s="2">
         <v>82</v>
       </c>
@@ -26302,18 +26346,16 @@
         <v>82</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>173</v>
+        <v>796</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>828</v>
+        <v>797</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>829</v>
+        <v>798</v>
       </c>
       <c r="N198" s="2"/>
-      <c r="O198" t="s" s="2">
-        <v>830</v>
-      </c>
+      <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
         <v>82</v>
       </c>
@@ -26337,13 +26379,13 @@
         <v>82</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="Y198" t="s" s="2">
-        <v>831</v>
+        <v>82</v>
       </c>
       <c r="Z198" t="s" s="2">
-        <v>832</v>
+        <v>82</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>82</v>
@@ -26361,31 +26403,31 @@
         <v>82</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>827</v>
+        <v>118</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI198" t="s" s="2">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>718</v>
+        <v>82</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN198" t="s" s="2">
-        <v>833</v>
+        <v>82</v>
       </c>
       <c r="AO198" t="s" s="2">
         <v>82</v>
@@ -26393,12 +26435,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>834</v>
+        <v>799</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>834</v>
-      </c>
-      <c r="C199" s="2"/>
+        <v>793</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>800</v>
+      </c>
       <c r="D199" t="s" s="2">
         <v>82</v>
       </c>
@@ -26419,18 +26463,16 @@
         <v>82</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>477</v>
+        <v>801</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>835</v>
+        <v>802</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>836</v>
+        <v>803</v>
       </c>
       <c r="N199" s="2"/>
-      <c r="O199" t="s" s="2">
-        <v>837</v>
-      </c>
+      <c r="O199" s="2"/>
       <c r="P199" t="s" s="2">
         <v>82</v>
       </c>
@@ -26478,31 +26520,31 @@
         <v>82</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>834</v>
+        <v>118</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI199" t="s" s="2">
-        <v>838</v>
+        <v>206</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>839</v>
+        <v>82</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM199" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>840</v>
+        <v>82</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>82</v>
@@ -26510,42 +26552,46 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>841</v>
+        <v>804</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
-        <v>82</v>
+        <v>805</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I200" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>390</v>
+        <v>111</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>842</v>
+        <v>806</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>843</v>
-      </c>
-      <c r="N200" s="2"/>
-      <c r="O200" s="2"/>
+        <v>807</v>
+      </c>
+      <c r="N200" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O200" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P200" t="s" s="2">
         <v>82</v>
       </c>
@@ -26593,25 +26639,25 @@
         <v>82</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>841</v>
+        <v>808</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI200" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>844</v>
+        <v>196</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM200" t="s" s="2">
         <v>82</v>
@@ -26625,10 +26671,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26651,19 +26697,17 @@
         <v>82</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>771</v>
+        <v>439</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>846</v>
+        <v>810</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>847</v>
-      </c>
-      <c r="N201" t="s" s="2">
-        <v>848</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="N201" s="2"/>
       <c r="O201" t="s" s="2">
-        <v>849</v>
+        <v>812</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>82</v>
@@ -26688,31 +26732,29 @@
         <v>82</v>
       </c>
       <c r="X201" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>82</v>
+        <v>813</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>82</v>
+        <v>814</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB201" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC201" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="AC201" s="2"/>
       <c r="AD201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE201" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -26727,16 +26769,16 @@
         <v>102</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>850</v>
+        <v>815</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>851</v>
+        <v>108</v>
       </c>
       <c r="AM201" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>82</v>
+        <v>816</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>82</v>
@@ -26744,12 +26786,14 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>852</v>
+        <v>817</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>852</v>
-      </c>
-      <c r="C202" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="C202" t="s" s="2">
+        <v>818</v>
+      </c>
       <c r="D202" t="s" s="2">
         <v>82</v>
       </c>
@@ -26770,16 +26814,18 @@
         <v>82</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>104</v>
+        <v>439</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>105</v>
+        <v>819</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>106</v>
+        <v>811</v>
       </c>
       <c r="N202" s="2"/>
-      <c r="O202" s="2"/>
+      <c r="O202" t="s" s="2">
+        <v>812</v>
+      </c>
       <c r="P202" t="s" s="2">
         <v>82</v>
       </c>
@@ -26803,13 +26849,11 @@
         <v>82</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y202" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y202" s="2"/>
       <c r="Z202" t="s" s="2">
-        <v>82</v>
+        <v>820</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>82</v>
@@ -26827,31 +26871,31 @@
         <v>82</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>107</v>
+        <v>809</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ202" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK202" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AL202" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL202" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM202" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>82</v>
+        <v>816</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>82</v>
@@ -26859,21 +26903,23 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>853</v>
+        <v>821</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>853</v>
-      </c>
-      <c r="C203" s="2"/>
+        <v>809</v>
+      </c>
+      <c r="C203" t="s" s="2">
+        <v>822</v>
+      </c>
       <c r="D203" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E203" s="2"/>
       <c r="F203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>82</v>
@@ -26885,18 +26931,18 @@
         <v>82</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>111</v>
+        <v>439</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>112</v>
+        <v>823</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O203" s="2"/>
+        <v>811</v>
+      </c>
+      <c r="N203" s="2"/>
+      <c r="O203" t="s" s="2">
+        <v>812</v>
+      </c>
       <c r="P203" t="s" s="2">
         <v>82</v>
       </c>
@@ -26920,13 +26966,11 @@
         <v>82</v>
       </c>
       <c r="X203" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y203" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y203" s="2"/>
       <c r="Z203" t="s" s="2">
-        <v>82</v>
+        <v>824</v>
       </c>
       <c r="AA203" t="s" s="2">
         <v>82</v>
@@ -26944,7 +26988,7 @@
         <v>82</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>118</v>
+        <v>809</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -26956,19 +27000,19 @@
         <v>82</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK203" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AL203" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL203" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM203" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>82</v>
+        <v>816</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>82</v>
@@ -26976,45 +27020,43 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>854</v>
+        <v>825</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>854</v>
+        <v>825</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>791</v>
+        <v>82</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I204" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>111</v>
+        <v>623</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>792</v>
+        <v>826</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>827</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" t="s" s="2">
-        <v>406</v>
+        <v>828</v>
       </c>
       <c r="P204" t="s" s="2">
         <v>82</v>
@@ -27063,31 +27105,31 @@
         <v>82</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK204" t="s" s="2">
-        <v>196</v>
+        <v>629</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM204" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>82</v>
+        <v>829</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>82</v>
@@ -27095,10 +27137,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>855</v>
+        <v>830</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>855</v>
+        <v>830</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27106,10 +27148,10 @@
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>82</v>
@@ -27121,19 +27163,19 @@
         <v>82</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>439</v>
+        <v>718</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>856</v>
+        <v>831</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>857</v>
+        <v>832</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>858</v>
+        <v>833</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>859</v>
+        <v>722</v>
       </c>
       <c r="P205" t="s" s="2">
         <v>82</v>
@@ -27158,13 +27200,13 @@
         <v>82</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y205" t="s" s="2">
-        <v>178</v>
+        <v>82</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>82</v>
@@ -27182,13 +27224,13 @@
         <v>82</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>855</v>
+        <v>830</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI205" t="s" s="2">
         <v>82</v>
@@ -27197,16 +27239,16 @@
         <v>102</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>860</v>
+        <v>723</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>861</v>
+        <v>108</v>
       </c>
       <c r="AM205" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>862</v>
+        <v>834</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>82</v>
@@ -27214,10 +27256,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>863</v>
+        <v>835</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>863</v>
+        <v>835</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27240,19 +27282,17 @@
         <v>82</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>600</v>
+        <v>836</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>864</v>
+        <v>837</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>865</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>866</v>
-      </c>
+        <v>838</v>
+      </c>
+      <c r="N206" s="2"/>
       <c r="O206" t="s" s="2">
-        <v>867</v>
+        <v>839</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>82</v>
@@ -27301,7 +27341,7 @@
         <v>82</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>863</v>
+        <v>835</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -27316,16 +27356,16 @@
         <v>102</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>868</v>
+        <v>757</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>869</v>
+        <v>108</v>
       </c>
       <c r="AM206" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>870</v>
+        <v>840</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>82</v>
@@ -27333,21 +27373,21 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>871</v>
+        <v>841</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>871</v>
+        <v>841</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
-        <v>872</v>
+        <v>82</v>
       </c>
       <c r="E207" s="2"/>
       <c r="F207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G207" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H207" t="s" s="2">
         <v>82</v>
@@ -27359,18 +27399,18 @@
         <v>82</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>873</v>
+        <v>173</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>874</v>
+        <v>842</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>875</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="O207" s="2"/>
+        <v>843</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" t="s" s="2">
+        <v>844</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>82</v>
       </c>
@@ -27394,13 +27434,13 @@
         <v>82</v>
       </c>
       <c r="X207" t="s" s="2">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="Y207" t="s" s="2">
-        <v>82</v>
+        <v>845</v>
       </c>
       <c r="Z207" t="s" s="2">
-        <v>82</v>
+        <v>846</v>
       </c>
       <c r="AA207" t="s" s="2">
         <v>82</v>
@@ -27418,13 +27458,13 @@
         <v>82</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>871</v>
+        <v>841</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH207" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI207" t="s" s="2">
         <v>82</v>
@@ -27433,7 +27473,7 @@
         <v>102</v>
       </c>
       <c r="AK207" t="s" s="2">
-        <v>877</v>
+        <v>732</v>
       </c>
       <c r="AL207" t="s" s="2">
         <v>108</v>
@@ -27442,7 +27482,7 @@
         <v>82</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>878</v>
+        <v>847</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>82</v>
@@ -27450,10 +27490,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>879</v>
+        <v>848</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>879</v>
+        <v>848</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27473,22 +27513,20 @@
         <v>82</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>880</v>
+        <v>477</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>881</v>
+        <v>849</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>882</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>883</v>
-      </c>
+        <v>850</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" t="s" s="2">
-        <v>884</v>
+        <v>851</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>82</v>
@@ -27537,7 +27575,7 @@
         <v>82</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>879</v>
+        <v>848</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -27546,22 +27584,22 @@
         <v>90</v>
       </c>
       <c r="AI208" t="s" s="2">
-        <v>82</v>
+        <v>852</v>
       </c>
       <c r="AJ208" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="AL208" t="s" s="2">
-        <v>885</v>
+        <v>108</v>
       </c>
       <c r="AM208" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN208" t="s" s="2">
-        <v>82</v>
+        <v>854</v>
       </c>
       <c r="AO208" t="s" s="2">
         <v>82</v>
@@ -27569,10 +27607,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>886</v>
+        <v>855</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>886</v>
+        <v>855</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27583,32 +27621,28 @@
         <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I209" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J209" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>771</v>
+        <v>390</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>887</v>
+        <v>856</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>888</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>890</v>
-      </c>
+        <v>857</v>
+      </c>
+      <c r="N209" s="2"/>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>82</v>
       </c>
@@ -27656,13 +27690,13 @@
         <v>82</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>886</v>
+        <v>855</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH209" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI209" t="s" s="2">
         <v>82</v>
@@ -27671,7 +27705,7 @@
         <v>102</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>891</v>
+        <v>858</v>
       </c>
       <c r="AL209" t="s" s="2">
         <v>108</v>
@@ -27688,10 +27722,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>892</v>
+        <v>859</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27702,7 +27736,7 @@
         <v>80</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>82</v>
@@ -27714,16 +27748,20 @@
         <v>82</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>104</v>
+        <v>785</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>105</v>
+        <v>860</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N210" s="2"/>
-      <c r="O210" s="2"/>
+        <v>861</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="O210" t="s" s="2">
+        <v>863</v>
+      </c>
       <c r="P210" t="s" s="2">
         <v>82</v>
       </c>
@@ -27771,25 +27809,25 @@
         <v>82</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>107</v>
+        <v>859</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH210" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI210" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK210" t="s" s="2">
-        <v>108</v>
+        <v>864</v>
       </c>
       <c r="AL210" t="s" s="2">
-        <v>82</v>
+        <v>865</v>
       </c>
       <c r="AM210" t="s" s="2">
         <v>82</v>
@@ -27803,21 +27841,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>893</v>
+        <v>866</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>893</v>
+        <v>866</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>82</v>
@@ -27829,17 +27867,15 @@
         <v>82</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N211" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N211" s="2"/>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
         <v>82</v>
@@ -27888,19 +27924,19 @@
         <v>82</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>108</v>
@@ -27920,14 +27956,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>894</v>
+        <v>867</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>791</v>
+        <v>110</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -27940,26 +27976,24 @@
         <v>82</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J212" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K212" t="s" s="2">
         <v>111</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>792</v>
+        <v>112</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>793</v>
+        <v>113</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="O212" t="s" s="2">
-        <v>406</v>
-      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>82</v>
       </c>
@@ -28007,7 +28041,7 @@
         <v>82</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>794</v>
+        <v>118</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -28022,7 +28056,7 @@
         <v>119</v>
       </c>
       <c r="AK212" t="s" s="2">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="AL212" t="s" s="2">
         <v>82</v>
@@ -28039,44 +28073,46 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>895</v>
+        <v>868</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
-        <v>82</v>
+        <v>805</v>
       </c>
       <c r="E213" s="2"/>
       <c r="F213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I213" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J213" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>896</v>
+        <v>111</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>897</v>
+        <v>806</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>898</v>
+        <v>807</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>899</v>
-      </c>
-      <c r="O213" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O213" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P213" t="s" s="2">
         <v>82</v>
       </c>
@@ -28124,31 +28160,31 @@
         <v>82</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>895</v>
+        <v>808</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH213" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ213" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK213" t="s" s="2">
-        <v>415</v>
+        <v>196</v>
       </c>
       <c r="AL213" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM213" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>900</v>
+        <v>82</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>82</v>
@@ -28156,10 +28192,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>901</v>
+        <v>869</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>901</v>
+        <v>869</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28179,19 +28215,23 @@
         <v>82</v>
       </c>
       <c r="J214" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>173</v>
+        <v>439</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>902</v>
+        <v>870</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>903</v>
-      </c>
-      <c r="N214" s="2"/>
-      <c r="O214" s="2"/>
+        <v>871</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>872</v>
+      </c>
+      <c r="O214" t="s" s="2">
+        <v>873</v>
+      </c>
       <c r="P214" t="s" s="2">
         <v>82</v>
       </c>
@@ -28215,13 +28255,13 @@
         <v>82</v>
       </c>
       <c r="X214" t="s" s="2">
-        <v>264</v>
+        <v>177</v>
       </c>
       <c r="Y214" t="s" s="2">
-        <v>903</v>
+        <v>178</v>
       </c>
       <c r="Z214" t="s" s="2">
-        <v>904</v>
+        <v>179</v>
       </c>
       <c r="AA214" t="s" s="2">
         <v>82</v>
@@ -28239,7 +28279,7 @@
         <v>82</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>901</v>
+        <v>869</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>90</v>
@@ -28254,23 +28294,1080 @@
         <v>102</v>
       </c>
       <c r="AK214" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="AL214" t="s" s="2">
+        <v>875</v>
+      </c>
+      <c r="AM214" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN214" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="AO214" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="215" hidden="true">
+      <c r="A215" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="B215" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="C215" s="2"/>
+      <c r="D215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E215" s="2"/>
+      <c r="F215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G215" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K215" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="L215" t="s" s="2">
+        <v>878</v>
+      </c>
+      <c r="M215" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="N215" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="O215" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="P215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q215" s="2"/>
+      <c r="R215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF215" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="AG215" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH215" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ215" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK215" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="AL215" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="AM215" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN215" t="s" s="2">
+        <v>884</v>
+      </c>
+      <c r="AO215" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="216" hidden="true">
+      <c r="A216" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="B216" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="C216" s="2"/>
+      <c r="D216" t="s" s="2">
+        <v>886</v>
+      </c>
+      <c r="E216" s="2"/>
+      <c r="F216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G216" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K216" t="s" s="2">
+        <v>887</v>
+      </c>
+      <c r="L216" t="s" s="2">
+        <v>888</v>
+      </c>
+      <c r="M216" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="N216" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="O216" s="2"/>
+      <c r="P216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q216" s="2"/>
+      <c r="R216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF216" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="AG216" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH216" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ216" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK216" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="AL216" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM216" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN216" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="AO216" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="217" hidden="true">
+      <c r="A217" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="B217" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="C217" s="2"/>
+      <c r="D217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E217" s="2"/>
+      <c r="F217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G217" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J217" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K217" t="s" s="2">
+        <v>894</v>
+      </c>
+      <c r="L217" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="M217" t="s" s="2">
+        <v>896</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>897</v>
+      </c>
+      <c r="O217" t="s" s="2">
+        <v>898</v>
+      </c>
+      <c r="P217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q217" s="2"/>
+      <c r="R217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF217" t="s" s="2">
+        <v>893</v>
+      </c>
+      <c r="AG217" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH217" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ217" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>853</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>901</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="N218" t="s" s="2">
+        <v>903</v>
+      </c>
+      <c r="O218" t="s" s="2">
+        <v>904</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>900</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK218" t="s" s="2">
         <v>905</v>
       </c>
-      <c r="AL214" t="s" s="2">
+      <c r="AL218" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AM214" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN214" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO214" t="s" s="2">
+      <c r="AM218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN218" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO218" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>906</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K219" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L219" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF219" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG219" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AK219" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN219" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO219" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="220" hidden="true">
+      <c r="A220" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K220" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M220" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N220" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O220" s="2"/>
+      <c r="P220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q220" s="2"/>
+      <c r="R220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF220" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH220" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ220" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK220" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AL220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN220" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO220" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="221" hidden="true">
+      <c r="A221" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J221" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K221" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="P221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q221" s="2"/>
+      <c r="R221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF221" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG221" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH221" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ221" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK221" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AL221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN221" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO221" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>910</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>911</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="N222" t="s" s="2">
+        <v>913</v>
+      </c>
+      <c r="O222" s="2"/>
+      <c r="P222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>909</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM222" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN222" t="s" s="2">
+        <v>914</v>
+      </c>
+      <c r="AO222" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="223" hidden="true">
+      <c r="A223" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="B223" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J223" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K223" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="L223" t="s" s="2">
+        <v>916</v>
+      </c>
+      <c r="M223" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q223" s="2"/>
+      <c r="R223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X223" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>917</v>
+      </c>
+      <c r="Z223" t="s" s="2">
+        <v>918</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="AG223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH223" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ223" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK223" t="s" s="2">
+        <v>919</v>
+      </c>
+      <c r="AL223" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN223" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO223" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO214">
+  <autoFilter ref="A1:AO223">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28280,7 +29377,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI213">
+  <conditionalFormatting sqref="A2:AI222">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
